--- a/artfynd/A 12545-2024 artfynd.xlsx
+++ b/artfynd/A 12545-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137391965</v>
       </c>
       <c r="B2" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137391966</v>
       </c>
       <c r="B3" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137391967</v>
       </c>
       <c r="B4" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>137391984</v>
       </c>
       <c r="B5" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12545-2024 artfynd.xlsx
+++ b/artfynd/A 12545-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137391965</v>
       </c>
       <c r="B2" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137391966</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137391967</v>
       </c>
       <c r="B4" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>137391984</v>
       </c>
       <c r="B5" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12545-2024 artfynd.xlsx
+++ b/artfynd/A 12545-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137391965</v>
       </c>
       <c r="B2" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137391966</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137391967</v>
       </c>
       <c r="B4" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>137391984</v>
       </c>
       <c r="B5" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12545-2024 artfynd.xlsx
+++ b/artfynd/A 12545-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137391965</v>
       </c>
       <c r="B2" t="n">
-        <v>99351</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137391966</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137391967</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>137391984</v>
       </c>
       <c r="B5" t="n">
-        <v>99469</v>
+        <v>99473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
